--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,200 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129375406</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98688</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>661422</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6684980</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Sonja Jederlund , Tore Dahlberg, Felicia Wikinger</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129375408</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105738</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>661490</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6684925</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Sonja Jederlund , Tore Dahlberg, Felicia Wikinger</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98688</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105738</v>
+        <v>105754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105754</v>
+        <v>105756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105756</v>
+        <v>105757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105757</v>
+        <v>105761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105761</v>
+        <v>105763</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105763</v>
+        <v>105767</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105767</v>
+        <v>105777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105777</v>
+        <v>105780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105780</v>
+        <v>105809</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105809</v>
+        <v>105821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91811</v>
+        <v>91812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105821</v>
+        <v>105822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129349665</v>
       </c>
       <c r="B2" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
+          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>129349663</v>
       </c>
       <c r="B3" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
+          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>129349658</v>
       </c>
       <c r="B4" t="n">
-        <v>91812</v>
+        <v>91817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
+          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>129375406</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129375408</v>
       </c>
       <c r="B6" t="n">
-        <v>105822</v>
+        <v>105827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Samuel Persson, Sonja Jederlund , Felicia Wikinger, Teo Jernkvist, Christian Luth</t>
+          <t>Tore Dahlberg, Christian Luth, Teo Jernkvist, Felicia Wikinger, Sonja Jederlund , Samuel Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,1032 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129922060</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91372</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>661485</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6684846</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129922064</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92012</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>715</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gloeoporus pannocinctus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Romell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>661492</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6684764</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129922044</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>661500</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6684732</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129922043</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>661500</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6684766</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129922095</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>661381</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6684927</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129922059</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90981</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>661530</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6684988</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129922039</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sevarsbolet, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>661473</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6684673</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129922063</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>661504</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6684736</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129922096</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>661384</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6684930</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1270,37 +1270,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129922064</v>
+        <v>129922044</v>
       </c>
       <c r="B8" t="n">
-        <v>92012</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>715</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1308,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661492</v>
+        <v>661500</v>
       </c>
       <c r="R8" t="n">
-        <v>6684764</v>
+        <v>6684732</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1343,7 +1352,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1353,7 +1362,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129922044</v>
+        <v>129922043</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,16 +1400,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1417,7 +1426,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1430,7 +1439,7 @@
         <v>661500</v>
       </c>
       <c r="R9" t="n">
-        <v>6684732</v>
+        <v>6684766</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1462,7 +1471,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1472,7 +1481,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,27 +1508,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129922043</v>
+        <v>129922095</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>5197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1527,29 +1536,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långåsen, Upl</t>
+          <t>Stormon, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661500</v>
+        <v>661381</v>
       </c>
       <c r="R10" t="n">
-        <v>6684766</v>
+        <v>6684927</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1581,7 +1587,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1591,7 +1597,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1624,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129922095</v>
+        <v>129922039</v>
       </c>
       <c r="B11" t="n">
         <v>5197</v>
@@ -1652,20 +1658,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stormon, Upl</t>
+          <t>Sevarsbolet, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661381</v>
+        <v>661473</v>
       </c>
       <c r="R11" t="n">
-        <v>6684927</v>
+        <v>6684673</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1697,7 +1703,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1707,7 +1713,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,32 +1740,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129922059</v>
+        <v>129922063</v>
       </c>
       <c r="B12" t="n">
-        <v>90981</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,14 +1774,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormon, Upl</t>
+          <t>Långåsen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661530</v>
+        <v>661504</v>
       </c>
       <c r="R12" t="n">
-        <v>6684988</v>
+        <v>6684736</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1807,7 +1813,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1817,7 +1823,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129922039</v>
+        <v>129922096</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1861,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,20 +1884,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sevarsbolet, Upl</t>
+          <t>Stormon, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661473</v>
+        <v>661384</v>
       </c>
       <c r="R13" t="n">
-        <v>6684673</v>
+        <v>6684930</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1923,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1933,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,51 +1966,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129922063</v>
+        <v>129922040</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långåsen, Upl</t>
+          <t>Stormon, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661504</v>
+        <v>661542</v>
       </c>
       <c r="R14" t="n">
-        <v>6684736</v>
+        <v>6684905</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2033,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2043,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,8 +2064,24 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2070,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129922096</v>
+        <v>129922062</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>91563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,32 +2109,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2114,13 +2136,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661384</v>
+        <v>661466</v>
       </c>
       <c r="R15" t="n">
-        <v>6684930</v>
+        <v>6685017</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2149,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2159,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,6 +2190,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2183,6 +2206,617 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129922064</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92012</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>715</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gloeoporus pannocinctus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>661492</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6684764</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På murken granlåga. Svag syrlig doft. Extremt små porer, knappt synliga för blotta ögat. Gulaktig linje mellan porer och "fruktkött". Hyfsat säker på artbestämningen men har för säkerhets skull tagit kollekt som ska mikroskoperas.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129922072</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>661248</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6685195</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129922059</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90981</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>661530</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6684988</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129922067</v>
+      </c>
+      <c r="B19" t="n">
+        <v>105856</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>661243</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6685144</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129922079</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92317</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stormon, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>661255</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6685185</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129922060</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129922044</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129922043</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129922063</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129922062</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>129922064</v>
       </c>
       <c r="B16" t="n">
-        <v>92012</v>
+        <v>92015</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129922059</v>
       </c>
       <c r="B18" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129922067</v>
       </c>
       <c r="B19" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>129922079</v>
       </c>
       <c r="B20" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129922060</v>
       </c>
       <c r="B7" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129922044</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129922043</v>
       </c>
       <c r="B9" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129922063</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129922062</v>
       </c>
       <c r="B15" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>129922064</v>
       </c>
       <c r="B16" t="n">
-        <v>92015</v>
+        <v>92018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129922059</v>
       </c>
       <c r="B18" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129922067</v>
       </c>
       <c r="B19" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>129922079</v>
       </c>
       <c r="B20" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129922060</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129922063</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129922062</v>
       </c>
       <c r="B15" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>129922064</v>
       </c>
       <c r="B16" t="n">
-        <v>92018</v>
+        <v>92019</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129922059</v>
       </c>
       <c r="B18" t="n">
-        <v>90987</v>
+        <v>90988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129922067</v>
       </c>
       <c r="B19" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>129922079</v>
       </c>
       <c r="B20" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129922060</v>
       </c>
       <c r="B7" t="n">
-        <v>91379</v>
+        <v>91396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129922063</v>
       </c>
       <c r="B12" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129922062</v>
       </c>
       <c r="B15" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>129922064</v>
       </c>
       <c r="B16" t="n">
-        <v>92019</v>
+        <v>92036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129922059</v>
       </c>
       <c r="B18" t="n">
-        <v>90988</v>
+        <v>91005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129922067</v>
       </c>
       <c r="B19" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>129922079</v>
       </c>
       <c r="B20" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129922060</v>
       </c>
       <c r="B7" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129922063</v>
       </c>
       <c r="B12" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129922062</v>
       </c>
       <c r="B15" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>129922064</v>
       </c>
       <c r="B16" t="n">
-        <v>92052</v>
+        <v>92054</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129922059</v>
       </c>
       <c r="B18" t="n">
-        <v>91021</v>
+        <v>91023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129922067</v>
       </c>
       <c r="B19" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>129922079</v>
       </c>
       <c r="B20" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51517-2025 artfynd.xlsx
+++ b/artfynd/A 51517-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129922060</v>
       </c>
       <c r="B7" t="n">
-        <v>91414</v>
+        <v>91501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129922044</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129922043</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>129922063</v>
       </c>
       <c r="B12" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129922062</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>129922064</v>
       </c>
       <c r="B16" t="n">
-        <v>92054</v>
+        <v>92141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129922059</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>91110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129922067</v>
       </c>
       <c r="B19" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>129922079</v>
       </c>
       <c r="B20" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
